--- a/Тест2/252.xlsx
+++ b/Тест2/252.xlsx
@@ -210,16 +210,16 @@
     <t xml:space="preserve">Musluk namuna olishdan oldin suv nima uchun bir necha daqiqa oqiziladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Idish ichini namlab olish uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muslukni sovitish va tozalash uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suvga xlor qo'shilishi uchun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suv bosimini kamaytirish uchun</t>
+    <t xml:space="preserve">Idish ichini oldindan namlab olish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muslukni sovitish va tozalab olish uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suvga xlor qo'shilishini ta'minlash uchun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suv bosimini kamaytirib qo'yish uchun</t>
   </si>
   <si>
     <t xml:space="preserve">Quvurda turib qolgan suv chiqib ketishi uchun</t>
@@ -252,19 +252,19 @@
     <t xml:space="preserve">Yopiq manbadan olingan namunaning yo'llanma xatida qo'shimcha nima ko'rsatiladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Suvdagi baliq turlari va hajmi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qushlar soni va uyalar joyi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daryo kengligi va oqim tezligi</t>
+    <t xml:space="preserve">Suvdagi baliq turlari va ularning hajmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qushlar soni va ularning uyalar joyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daryo kengligi va oqim tezligi qiymati</t>
   </si>
   <si>
     <t xml:space="preserve">Manba turi: musluk, quduq yoki rezervuar</t>
   </si>
   <si>
-    <t xml:space="preserve">Havza turi va qirg'oq chuqurligi</t>
+    <t xml:space="preserve">Havza turi va qirg'oq chuqurligi o'lchami</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Manba turi: musluk, quduq yoki rezervuar. Xatda suv manbaining turi (musluk, quduq, rezervuar), tizim tavsifi va xlor qoldig'i (o'lchangan bo'lsa) qayd etiladi. Manba: Mavzu materiali (252.docx); WHO. Guidelines for drinking-water quality, 4-nashr, 1-ilova bilan (2017).</t>
